--- a/list_datapoints.xlsx
+++ b/list_datapoints.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\u0138303\PycharmProjects\StorageOptimisationImbalance\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kuleuven-my.sharepoint.com/personal/ruben_smets1_kuleuven_be/Documents/Github/StorageOptimisationImbalance/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="53" documentId="11_AD4E0353EBC228F67939954FBAB99FC8913E45B1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D6FB9C49-54BF-4C0A-B76D-C17621EF3884}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="19470" windowHeight="6465"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,23 +20,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="57">
   <si>
     <t>Data point</t>
   </si>
@@ -106,12 +96,6 @@
     <t>alpha</t>
   </si>
   <si>
-    <t>POS</t>
-  </si>
-  <si>
-    <t>NEG</t>
-  </si>
-  <si>
     <t>ACE</t>
   </si>
   <si>
@@ -127,9 +111,6 @@
     <t>Conventional generation forecast</t>
   </si>
   <si>
-    <t>RES forecast</t>
-  </si>
-  <si>
     <t>Wind offshore</t>
   </si>
   <si>
@@ -169,9 +150,6 @@
     <t>Price level per volume</t>
   </si>
   <si>
-    <t xml:space="preserve">Per step of 100MW between -1000 and +1000MW price point </t>
-  </si>
-  <si>
     <t>API ready</t>
   </si>
   <si>
@@ -187,20 +165,44 @@
     <t>H-2 is closest available in 15min resolution. However, there is one-minute imbalance price of H-1</t>
   </si>
   <si>
-    <t>ok, I think</t>
-  </si>
-  <si>
     <t>available up to H-4</t>
   </si>
   <si>
     <t>Not found</t>
+  </si>
+  <si>
+    <t>Individual bids --&gt; price, quantity, product</t>
+  </si>
+  <si>
+    <t>Imbalance price</t>
+  </si>
+  <si>
+    <t>RES</t>
+  </si>
+  <si>
+    <t>Wind offshore FC</t>
+  </si>
+  <si>
+    <t>Wind onshore FC</t>
+  </si>
+  <si>
+    <t>PV FC</t>
+  </si>
+  <si>
+    <t>LA/LB</t>
+  </si>
+  <si>
+    <t>LB</t>
+  </si>
+  <si>
+    <t>LA &amp; LB</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -212,6 +214,13 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -237,7 +246,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -246,6 +255,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -559,18 +573,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G1048576"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.88671875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.7109375" customWidth="1"/>
-    <col min="4" max="4" width="16.7109375" customWidth="1"/>
-    <col min="6" max="6" width="114.7109375" customWidth="1"/>
+    <col min="3" max="4" width="17.6640625" customWidth="1"/>
+    <col min="5" max="5" width="16.6640625" customWidth="1"/>
+    <col min="7" max="7" width="114.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -581,110 +595,128 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>45</v>
-      </c>
       <c r="F1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="3"/>
-      <c r="B3" t="s">
+      <c r="C2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="5"/>
+      <c r="B3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" t="s">
-        <v>46</v>
-      </c>
-      <c r="F3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="3"/>
-      <c r="B4" t="s">
+      <c r="C3" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="5"/>
+      <c r="B4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E4" t="s">
-        <v>46</v>
-      </c>
-      <c r="F4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="3"/>
-      <c r="B5" t="s">
+      <c r="C4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="5"/>
+      <c r="B5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F5" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="3"/>
-      <c r="B6" t="s">
+      <c r="C5" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="5"/>
+      <c r="B6" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E6" t="s">
-        <v>46</v>
-      </c>
-      <c r="F6" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C6" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B7" t="s">
         <v>13</v>
@@ -692,14 +724,17 @@
       <c r="C7" t="s">
         <v>5</v>
       </c>
-      <c r="D7" t="s">
-        <v>16</v>
+      <c r="D7" s="6" t="s">
+        <v>56</v>
       </c>
       <c r="E7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="F7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="3"/>
       <c r="B8" t="s">
         <v>14</v>
@@ -707,14 +742,17 @@
       <c r="C8" t="s">
         <v>5</v>
       </c>
-      <c r="D8" t="s">
-        <v>16</v>
+      <c r="D8" s="6" t="s">
+        <v>56</v>
       </c>
       <c r="E8" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="F8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="3"/>
       <c r="B9" t="s">
         <v>15</v>
@@ -722,14 +760,17 @@
       <c r="C9" t="s">
         <v>5</v>
       </c>
-      <c r="D9" t="s">
-        <v>16</v>
+      <c r="D9" s="6" t="s">
+        <v>56</v>
       </c>
       <c r="E9" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="F9" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>17</v>
       </c>
@@ -739,17 +780,20 @@
       <c r="C10" t="s">
         <v>5</v>
       </c>
-      <c r="D10" t="s">
-        <v>6</v>
+      <c r="D10" s="6" t="s">
+        <v>55</v>
       </c>
       <c r="E10" t="s">
-        <v>46</v>
+        <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+      <c r="G10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="3"/>
       <c r="B11" t="s">
         <v>19</v>
@@ -757,35 +801,41 @@
       <c r="C11" t="s">
         <v>5</v>
       </c>
-      <c r="D11" t="s">
-        <v>6</v>
+      <c r="D11" s="6" t="s">
+        <v>55</v>
       </c>
       <c r="E11" t="s">
-        <v>46</v>
+        <v>6</v>
       </c>
       <c r="F11" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+      <c r="G11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="3"/>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C12" t="s">
         <v>5</v>
       </c>
-      <c r="D12" t="s">
-        <v>6</v>
+      <c r="D12" s="6" t="s">
+        <v>55</v>
       </c>
       <c r="E12" t="s">
-        <v>46</v>
+        <v>6</v>
       </c>
       <c r="F12" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+      <c r="G12" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="3"/>
       <c r="B13" t="s">
         <v>20</v>
@@ -793,17 +843,20 @@
       <c r="C13" t="s">
         <v>5</v>
       </c>
-      <c r="D13" t="s">
-        <v>6</v>
+      <c r="D13" s="6" t="s">
+        <v>55</v>
       </c>
       <c r="E13" t="s">
-        <v>46</v>
+        <v>6</v>
       </c>
       <c r="F13" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+      <c r="G13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="3"/>
       <c r="B14" t="s">
         <v>21</v>
@@ -811,17 +864,20 @@
       <c r="C14" t="s">
         <v>5</v>
       </c>
-      <c r="D14" t="s">
-        <v>6</v>
+      <c r="D14" s="6" t="s">
+        <v>55</v>
       </c>
       <c r="E14" t="s">
-        <v>46</v>
+        <v>6</v>
       </c>
       <c r="F14" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+      <c r="G14" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="3"/>
       <c r="B15" t="s">
         <v>22</v>
@@ -829,224 +885,293 @@
       <c r="C15" t="s">
         <v>5</v>
       </c>
-      <c r="D15" t="s">
-        <v>6</v>
+      <c r="D15" s="6" t="s">
+        <v>55</v>
       </c>
       <c r="E15" t="s">
-        <v>46</v>
+        <v>6</v>
       </c>
       <c r="F15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+      <c r="G15" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="3"/>
       <c r="B16" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="C16" t="s">
         <v>5</v>
       </c>
-      <c r="D16" t="s">
-        <v>6</v>
+      <c r="D16" s="6" t="s">
+        <v>55</v>
       </c>
       <c r="E16" t="s">
+        <v>6</v>
+      </c>
+      <c r="F16" t="s">
+        <v>42</v>
+      </c>
+      <c r="G16" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" t="s">
+        <v>5</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="E17" t="s">
+        <v>6</v>
+      </c>
+      <c r="G17" t="s">
         <v>46</v>
       </c>
-      <c r="F16" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="3"/>
-      <c r="B17" t="s">
-        <v>24</v>
-      </c>
-      <c r="C17" t="s">
-        <v>5</v>
-      </c>
-      <c r="D17" t="s">
-        <v>6</v>
-      </c>
-      <c r="E17" t="s">
-        <v>46</v>
-      </c>
-      <c r="F17" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="3"/>
+      <c r="B18" t="s">
         <v>26</v>
       </c>
-      <c r="B18" t="s">
-        <v>27</v>
-      </c>
       <c r="C18" t="s">
         <v>5</v>
       </c>
-      <c r="D18" t="s">
-        <v>6</v>
-      </c>
-      <c r="F18" t="s">
+      <c r="D18" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="E18" t="s">
+        <v>16</v>
+      </c>
+      <c r="G18" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B19" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="3"/>
-      <c r="B19" t="s">
-        <v>28</v>
-      </c>
       <c r="C19" t="s">
         <v>5</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D19" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="E19" t="s">
         <v>16</v>
       </c>
       <c r="F19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" s="3"/>
+      <c r="B20" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B20" t="s">
-        <v>31</v>
-      </c>
       <c r="C20" t="s">
         <v>5</v>
       </c>
-      <c r="D20" t="s">
-        <v>16</v>
+      <c r="D20" s="6" t="s">
+        <v>56</v>
       </c>
       <c r="E20" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="F20" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="3"/>
       <c r="B21" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="C21" t="s">
         <v>5</v>
       </c>
-      <c r="D21" t="s">
-        <v>16</v>
+      <c r="D21" s="6" t="s">
+        <v>56</v>
       </c>
       <c r="E21" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="F21" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="3"/>
       <c r="B22" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C22" t="s">
         <v>5</v>
       </c>
-      <c r="D22" t="s">
-        <v>16</v>
+      <c r="D22" s="6" t="s">
+        <v>55</v>
       </c>
       <c r="E22" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
-        <v>39</v>
-      </c>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" s="3"/>
       <c r="B23" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C23" t="s">
-        <v>40</v>
-      </c>
-      <c r="D23" t="s">
-        <v>16</v>
-      </c>
-      <c r="F23" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="E23" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="3"/>
       <c r="B24" t="s">
+        <v>30</v>
+      </c>
+      <c r="C24" t="s">
+        <v>5</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="E24" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C25" t="s">
+        <v>37</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="E25" t="s">
+        <v>16</v>
+      </c>
+      <c r="G25" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" s="3"/>
+      <c r="B26" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" s="3"/>
+      <c r="B27" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" s="3"/>
+      <c r="B28" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" s="3"/>
+      <c r="B29" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C29" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" t="s">
         <v>40</v>
       </c>
-      <c r="D24" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="3"/>
-      <c r="B25" t="s">
-        <v>36</v>
-      </c>
-      <c r="C25" t="s">
-        <v>40</v>
-      </c>
-      <c r="D25" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="3"/>
-      <c r="B26" t="s">
-        <v>37</v>
-      </c>
-      <c r="C26" t="s">
-        <v>40</v>
-      </c>
-      <c r="D26" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="3"/>
-      <c r="B27" t="s">
-        <v>38</v>
-      </c>
-      <c r="C27" t="s">
-        <v>40</v>
-      </c>
-      <c r="D27" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B28" t="s">
-        <v>43</v>
-      </c>
-      <c r="C28" t="s">
-        <v>5</v>
-      </c>
-      <c r="D28" t="s">
-        <v>16</v>
-      </c>
-      <c r="E28" t="s">
-        <v>50</v>
-      </c>
-      <c r="F28" t="s">
-        <v>44</v>
-      </c>
+      <c r="C30" t="s">
+        <v>5</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="E30" t="s">
+        <v>16</v>
+      </c>
+      <c r="F30" t="s">
+        <v>42</v>
+      </c>
+      <c r="G30" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="1048576" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D1048576" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A23:A27"/>
+    <mergeCell ref="A25:A29"/>
     <mergeCell ref="A2:A6"/>
     <mergeCell ref="A7:A9"/>
-    <mergeCell ref="A10:A17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="A20:A22"/>
+    <mergeCell ref="A10:A16"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="A19:A24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
